--- a/pantallas_android/tipo_equipos.xlsx
+++ b/pantallas_android/tipo_equipos.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5555E9A7-E666-4EA8-AAB5-5E05032FE0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="83">
   <si>
     <t xml:space="preserve">BOMBA                         </t>
   </si>
@@ -270,7 +271,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -312,14 +313,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -357,7 +361,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -429,7 +433,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -602,7 +606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -899,6 +903,9 @@
       <c r="A43" t="s">
         <v>36</v>
       </c>
+      <c r="C43" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -992,6 +999,9 @@
       <c r="A61" t="s">
         <v>51</v>
       </c>
+      <c r="C61" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
@@ -1038,6 +1048,9 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>56</v>
+      </c>
+      <c r="C67" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1070,7 +1083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1079,7 +1092,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/pantallas_android/tipo_equipos.xlsx
+++ b/pantallas_android/tipo_equipos.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5555E9A7-E666-4EA8-AAB5-5E05032FE0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="componentes" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
@@ -17,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="166">
   <si>
     <t xml:space="preserve">BOMBA                         </t>
   </si>
@@ -266,14 +265,271 @@
   </si>
   <si>
     <t>UNIDAD MANEJADORA AGUA HELADA</t>
+  </si>
+  <si>
+    <t>Clasificacion</t>
+  </si>
+  <si>
+    <t>Minisplit Expansion Directa</t>
+  </si>
+  <si>
+    <t>Cassette Expansion Directa</t>
+  </si>
+  <si>
+    <t>Piso-Techo Expansion Directa</t>
+  </si>
+  <si>
+    <t>Paquete / Rooftop Expansion Directa</t>
+  </si>
+  <si>
+    <t>Unidad condensadora VRF/VRV</t>
+  </si>
+  <si>
+    <t>Cassette VRF/VRV</t>
+  </si>
+  <si>
+    <t>Conducto VRF/VRV</t>
+  </si>
+  <si>
+    <t>Piso-Techo VRF/VRV</t>
+  </si>
+  <si>
+    <t>Tipo mural VRF/VRV</t>
+  </si>
+  <si>
+    <t>Chiller enfriado por Aire</t>
+  </si>
+  <si>
+    <t>Chiller enfriado por Agua</t>
+  </si>
+  <si>
+    <t>Fan Coil Unit (FCU)</t>
+  </si>
+  <si>
+    <t>Cassette hidrónico</t>
+  </si>
+  <si>
+    <t>AHU / UMA</t>
+  </si>
+  <si>
+    <t>Extractor axial</t>
+  </si>
+  <si>
+    <t>Extractor centrífugo</t>
+  </si>
+  <si>
+    <t>Ventilador axial</t>
+  </si>
+  <si>
+    <t>Ventilador centrífugo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tablero de Control DDC </t>
+  </si>
+  <si>
+    <t>Direct Digital Control</t>
+  </si>
+  <si>
+    <t>Bomba de agua helada</t>
+  </si>
+  <si>
+    <t>Bomba de agua de condensación</t>
+  </si>
+  <si>
+    <t>Torre de enfriamiento abierta</t>
+  </si>
+  <si>
+    <t>Torre de enfriamiento cerrada</t>
+  </si>
+  <si>
+    <t>Cuarto Frio</t>
+  </si>
+  <si>
+    <t>Vitrina</t>
+  </si>
+  <si>
+    <t>Congelador</t>
+  </si>
+  <si>
+    <t>Rack de Compresores</t>
+  </si>
+  <si>
+    <t>Unidad Evaporadora</t>
+  </si>
+  <si>
+    <t>cámara frigorífica</t>
+  </si>
+  <si>
+    <t>Camara de Conservacion</t>
+  </si>
+  <si>
+    <t>Camara de Congelacion</t>
+  </si>
+  <si>
+    <t>Tipo de Equipos investigados</t>
+  </si>
+  <si>
+    <t>Unidad de Ventilacion</t>
+  </si>
+  <si>
+    <t>Campana Extractora</t>
+  </si>
+  <si>
+    <t>ventilacion</t>
+  </si>
+  <si>
+    <t>Aclarar si es un sensor es componente y si es un tablaro es un equipo</t>
+  </si>
+  <si>
+    <t>Cortina de Aire</t>
+  </si>
+  <si>
+    <t>Caja de Volumen Variable (VAV o CVV)</t>
+  </si>
+  <si>
+    <t>Dispensador de Agua</t>
+  </si>
+  <si>
+    <t>fancoilt agua helada</t>
+  </si>
+  <si>
+    <t>IdComponente</t>
+  </si>
+  <si>
+    <t>TipoComponente</t>
+  </si>
+  <si>
+    <t>NombreComponente</t>
+  </si>
+  <si>
+    <t>Componente</t>
+  </si>
+  <si>
+    <t>Equipo / General</t>
+  </si>
+  <si>
+    <t>Válvula</t>
+  </si>
+  <si>
+    <t>Compresor</t>
+  </si>
+  <si>
+    <t>Control / Sensor</t>
+  </si>
+  <si>
+    <t>Bandas / Poleas</t>
+  </si>
+  <si>
+    <t>Bomba</t>
+  </si>
+  <si>
+    <t>Rodamientos / Chumaceras</t>
+  </si>
+  <si>
+    <t>Ventilador / Blower / Turbinas</t>
+  </si>
+  <si>
+    <t>Compresor #1</t>
+  </si>
+  <si>
+    <t>Compresor #2</t>
+  </si>
+  <si>
+    <t>Ductos</t>
+  </si>
+  <si>
+    <t>Filtro</t>
+  </si>
+  <si>
+    <t>Unidad manejadora (UMA/AHU)</t>
+  </si>
+  <si>
+    <t>Serpentín</t>
+  </si>
+  <si>
+    <t>Drenaje / Bandeja / Dampers</t>
+  </si>
+  <si>
+    <t>Circuito de agua helada</t>
+  </si>
+  <si>
+    <t>Motor condensador</t>
+  </si>
+  <si>
+    <t>Compresor #3</t>
+  </si>
+  <si>
+    <t>Compresor #4</t>
+  </si>
+  <si>
+    <t>Sepertin Condensador</t>
+  </si>
+  <si>
+    <t>Sepertin Evaporador</t>
+  </si>
+  <si>
+    <t>Válvula Termostática TXV</t>
+  </si>
+  <si>
+    <t>Válvula Electrónica EEV</t>
+  </si>
+  <si>
+    <t>Motor de Oscilacion (Louver)</t>
+  </si>
+  <si>
+    <t>Tarjeta de control (PCB)</t>
+  </si>
+  <si>
+    <t>Capacitor de arranque</t>
+  </si>
+  <si>
+    <t>Cajas de Selección de Modo (BS Box)</t>
+  </si>
+  <si>
+    <t>Tarjeta principal de comunicación RS-485</t>
+  </si>
+  <si>
+    <t>Tarjeta inteligente local</t>
+  </si>
+  <si>
+    <t>Bomba de condensado integrada</t>
+  </si>
+  <si>
+    <t>Tarjeta Transmisora</t>
+  </si>
+  <si>
+    <t>Unidades Scroll</t>
+  </si>
+  <si>
+    <t>Screw (Tornillo) o Centrífugas</t>
+  </si>
+  <si>
+    <t>Evaporador (Intercambiador)</t>
+  </si>
+  <si>
+    <t>Panel de Control Central (PLC, DDC o Termostato Inteligente)</t>
+  </si>
+  <si>
+    <t>Sensor de Temperatura</t>
+  </si>
+  <si>
+    <t>Sensor de Humedad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -301,8 +557,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -321,9 +581,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -361,7 +621,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -433,7 +693,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -606,18 +866,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E71"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" customWidth="1"/>
-    <col min="3" max="3" width="38.28515625" customWidth="1"/>
-    <col min="4" max="4" width="33.7109375" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="29.28515625" customWidth="1"/>
+    <col min="7" max="7" width="34.7109375" customWidth="1"/>
+    <col min="8" max="8" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>60</v>
       </c>
@@ -633,265 +896,481 @@
       <c r="E1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>67</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
       <c r="C17" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
       <c r="C21" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
       <c r="B24" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
       <c r="D25" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
       <c r="C26" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>69</v>
       </c>
       <c r="C28" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" t="s">
+        <v>112</v>
+      </c>
+      <c r="H29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" t="s">
+        <v>114</v>
+      </c>
+      <c r="H30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33" t="s">
+        <v>118</v>
+      </c>
+      <c r="H33" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>28</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G34" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G36" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>35</v>
       </c>
@@ -899,7 +1378,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>36</v>
       </c>
@@ -907,77 +1386,119 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C54" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>49</v>
       </c>
@@ -985,17 +1506,23 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>51</v>
       </c>
@@ -1003,7 +1530,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>52</v>
       </c>
@@ -1011,15 +1538,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>53</v>
       </c>
       <c r="B63" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>54</v>
       </c>
@@ -1083,16 +1613,439 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C28" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
